--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/phi-4/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/phi-4/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="D2">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="G2">
-        <v>126</v>
+        <v>71</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="H3">
         <v>426</v>
